--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SOQUETE FAROL - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SOQUETE FAROL - 02_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -507,22 +499,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7893986435675</t>
+          <t>7899468091384</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REPARO CHICOTE PEÇA+ TITAN/ YBR/ YES</t>
+          <t>SOQUETE FAROL MHX POP100 2007 A 2015/ BIZ125 2009 A 2010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -532,12 +519,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7893986435583</t>
+          <t>7898955470039</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REPARO CHICOTE PEÇA+ BIZ/ POP/ TITAN/ YES</t>
+          <t>SOQUETE FAROL BHD TITAN CG125/ TITAN150</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -545,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -553,20 +539,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7908305613297</t>
+          <t>7893986087188</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONECTOR 4 PINOS MHX </t>
+          <t>SOQUETE FAROL PEÇA+</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -574,12 +559,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7899468091384</t>
+          <t>7893986134004</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SOQUETE FAROL MHX POP100 2007 A 2015/ BIZ125 2009 A 2010</t>
+          <t>SOQUETE FAROL PEÇA+ BIZ100/ WEB100/ POP100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -587,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -595,79 +579,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7898955470039</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SOQUETE FAROL BHD TITAN CG125/ TITAN150</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7893986087188</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SOQUETE FAROL PEÇA+</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7893986134004</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SOQUETE FAROL PEÇA+ BIZ100/ WEB100/ POP100</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t> </t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
